--- a/Result/profitability/4171.xlsx
+++ b/Result/profitability/4171.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM58"/>
+  <dimension ref="A1:AM59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7796,6 +7796,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4171</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>60</v>
+      </c>
+      <c r="D59" t="n">
+        <v>12</v>
+      </c>
+      <c r="E59" t="n">
+        <v>48</v>
+      </c>
+      <c r="F59" t="n">
+        <v>80.33</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-14.08%</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>3</v>
+      </c>
+      <c r="J59" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-0.39875</v>
+      </c>
+      <c r="N59" t="n">
+        <v>68.88</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0.01999999999999999</v>
+      </c>
+      <c r="X59" t="n">
+        <v>-0.2222222222222221</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>8.530000000000001</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0.1188022284122563</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>-0.9396551724137931</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>6.879999999999995</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.09366916269571135</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK59" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
